--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D290"/>
+  <dimension ref="A1:D291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5644,6 +5644,24 @@
         <v>434.94</v>
       </c>
       <c r="D290" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>393.72</v>
+      </c>
+      <c r="C291" t="n">
+        <v>440.74</v>
+      </c>
+      <c r="D291" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5660,7 +5678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B307"/>
+  <dimension ref="A1:B308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8733,6 +8751,16 @@
       </c>
       <c r="B307" t="n">
         <v>-0.24</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>-0.91</v>
       </c>
     </row>
   </sheetData>
@@ -8901,28 +8929,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09418480214478474</v>
+        <v>-0.09480353745095597</v>
       </c>
       <c r="J2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K2" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05698524389667581</v>
+        <v>0.05812296465890621</v>
       </c>
       <c r="M2" t="n">
-        <v>2.400351283908992</v>
+        <v>2.395136190733763</v>
       </c>
       <c r="N2" t="n">
-        <v>9.213444966873407</v>
+        <v>9.184606845415702</v>
       </c>
       <c r="O2" t="n">
-        <v>3.035365705623197</v>
+        <v>3.030611628931642</v>
       </c>
       <c r="P2" t="n">
-        <v>397.1783099830076</v>
+        <v>397.1842053985793</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -8979,28 +9007,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2589756397858153</v>
+        <v>0.2641617299116358</v>
       </c>
       <c r="J3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L3" t="n">
-        <v>0.079918470769061</v>
+        <v>0.08319342738945734</v>
       </c>
       <c r="M3" t="n">
-        <v>5.19629567659247</v>
+        <v>5.204957922953463</v>
       </c>
       <c r="N3" t="n">
-        <v>47.27078785669648</v>
+        <v>47.30495129194402</v>
       </c>
       <c r="O3" t="n">
-        <v>6.875375470234078</v>
+        <v>6.877859499287843</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1749665411666</v>
+        <v>426.1244394313803</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9038,7 +9066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D290"/>
+  <dimension ref="A1:D291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15409,6 +15437,28 @@
         </is>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-10 22:17:07+00:00</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>-34.72571253839063,173.09389988129882</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>-34.72526925153458,173.09478403542622</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D291"/>
+  <dimension ref="A1:D294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5662,6 +5662,60 @@
         <v>440.74</v>
       </c>
       <c r="D291" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>394.02</v>
+      </c>
+      <c r="C292" t="n">
+        <v>439.14</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>394.07</v>
+      </c>
+      <c r="C293" t="n">
+        <v>440.27</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:17:28+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>393.73</v>
+      </c>
+      <c r="C294" t="n">
+        <v>440.27</v>
+      </c>
+      <c r="D294" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5678,7 +5732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B308"/>
+  <dimension ref="A1:B311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8761,6 +8815,36 @@
       </c>
       <c r="B308" t="n">
         <v>-0.91</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -8929,28 +9013,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09480353745095597</v>
+        <v>-0.09613248494393649</v>
       </c>
       <c r="J2" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K2" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05812296465890621</v>
+        <v>0.06101209298423138</v>
       </c>
       <c r="M2" t="n">
-        <v>2.395136190733763</v>
+        <v>2.377063237193933</v>
       </c>
       <c r="N2" t="n">
-        <v>9.184606845415702</v>
+        <v>9.095387694589906</v>
       </c>
       <c r="O2" t="n">
-        <v>3.030611628931642</v>
+        <v>3.015856046728674</v>
       </c>
       <c r="P2" t="n">
-        <v>397.1842053985793</v>
+        <v>397.1969271399385</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9007,28 +9091,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2641617299116358</v>
+        <v>0.2774010852526416</v>
       </c>
       <c r="J3" t="n">
+        <v>293</v>
+      </c>
+      <c r="K3" t="n">
         <v>290</v>
       </c>
-      <c r="K3" t="n">
-        <v>287</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.08319342738945734</v>
+        <v>0.09222034181411021</v>
       </c>
       <c r="M3" t="n">
-        <v>5.204957922953463</v>
+        <v>5.220773775698116</v>
       </c>
       <c r="N3" t="n">
-        <v>47.30495129194402</v>
+        <v>47.25877798635064</v>
       </c>
       <c r="O3" t="n">
-        <v>6.877859499287843</v>
+        <v>6.874502017335557</v>
       </c>
       <c r="P3" t="n">
-        <v>426.1244394313803</v>
+        <v>425.9948705574872</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9066,7 +9150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D291"/>
+  <dimension ref="A1:D294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15459,6 +15543,72 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-03 22:17:14+00:00</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>-34.72570983402115,173.09389979298282</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>-34.72528367483702,173.09478450654075</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:17:20+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>-34.725709383292916,173.09389977826348</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>-34.72527348837967,173.0947841738161</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-27 22:17:28+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>-34.72571244824497,173.09389987835496</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>-34.72527348837967,173.0947841738161</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0015/nzd0015.xlsx
+++ b/data/nzd0015/nzd0015.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5713,9 +5713,27 @@
         <v>393.73</v>
       </c>
       <c r="C294" t="n">
-        <v>440.27</v>
+        <v>435.19</v>
       </c>
       <c r="D294" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="C295" t="n">
+        <v>432.53</v>
+      </c>
+      <c r="D295" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -5732,7 +5750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B311"/>
+  <dimension ref="A1:B312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8845,6 +8863,16 @@
       </c>
       <c r="B311" t="n">
         <v>0.03</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -9013,28 +9041,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.09613248494393649</v>
+        <v>-0.0975595277659428</v>
       </c>
       <c r="J2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06101209298423138</v>
+        <v>0.0630885526159477</v>
       </c>
       <c r="M2" t="n">
-        <v>2.377063237193933</v>
+        <v>2.375882254034424</v>
       </c>
       <c r="N2" t="n">
-        <v>9.095387694589906</v>
+        <v>9.080730192200321</v>
       </c>
       <c r="O2" t="n">
-        <v>3.015856046728674</v>
+        <v>3.013424993624418</v>
       </c>
       <c r="P2" t="n">
-        <v>397.1969271399385</v>
+        <v>397.2106567715694</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -9091,28 +9119,28 @@
         <v>0.026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2774010852526416</v>
+        <v>0.2734018273593977</v>
       </c>
       <c r="J3" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09222034181411021</v>
+        <v>0.09073701249205846</v>
       </c>
       <c r="M3" t="n">
-        <v>5.220773775698116</v>
+        <v>5.187907698417751</v>
       </c>
       <c r="N3" t="n">
-        <v>47.25877798635064</v>
+        <v>46.95019167269962</v>
       </c>
       <c r="O3" t="n">
-        <v>6.874502017335557</v>
+        <v>6.852020991846101</v>
       </c>
       <c r="P3" t="n">
-        <v>425.9948705574872</v>
+        <v>426.0340795132036</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -9150,7 +9178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D294"/>
+  <dimension ref="A1:D295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15600,10 +15628,32 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>-34.72527348837967,173.0947841738161</t>
+          <t>-34.72531928236479,173.09478566960547</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:17:40+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>-34.72572452776195,173.09390027283314</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>-34.72534326110486,173.09478645283446</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
